--- a/relatorios/clientes_cobranca.xlsx
+++ b/relatorios/clientes_cobranca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RPA\relatorios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131614F3-DED3-4714-85A8-551E7DA83060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE409FA2-CAE9-40BA-98EF-9C9E7D2C6189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,38 +37,38 @@
     <t>valor a ser pago</t>
   </si>
   <si>
-    <t>Carlos Eduardo Silva</t>
-  </si>
-  <si>
-    <t>carlos.silva@email.com</t>
-  </si>
-  <si>
     <t>R$ 250,50</t>
   </si>
   <si>
-    <t>Mariana Souza</t>
-  </si>
-  <si>
-    <t>mariana.souza@email.com</t>
-  </si>
-  <si>
     <t>R$ 480,00</t>
   </si>
   <si>
-    <t>Roberto Alves</t>
-  </si>
-  <si>
-    <t>roberto.alves@email.com</t>
-  </si>
-  <si>
     <t>R$ 135,90</t>
+  </si>
+  <si>
+    <t>leonardo.andrade@aluno.fmpsc.edu.br</t>
+  </si>
+  <si>
+    <t>lucas.blank@aluno.fmpsc.edu.br</t>
+  </si>
+  <si>
+    <t>Lucas Blank</t>
+  </si>
+  <si>
+    <t>Leonardo Souza</t>
+  </si>
+  <si>
+    <t>davi.lima@aluno.fmpsc.edu.br</t>
+  </si>
+  <si>
+    <t>Davi Lima</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +91,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444746"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -112,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -129,13 +140,17 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" style="3" customWidth="1"/>
@@ -448,7 +463,7 @@
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,67 +480,68 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4">
         <v>554899667714</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="C2" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="2">
         <v>46023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5">
         <v>554896403301</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2">
         <v>45658</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="6">
         <v>554898280959</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2">
         <v>45658</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="D5" s="7"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="B7" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="7"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="D10" s="7"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="D16" s="7"/>
     </row>
   </sheetData>
